--- a/Preencher/nba_2025_26_jogos_gameid.xlsx
+++ b/Preencher/nba_2025_26_jogos_gameid.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/db44bf30ba5480d8/Documentos/Python Scripts/Fantasy/Preencher/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="8_{0AAFFBA4-7A17-4274-9ECD-974DB7A7961E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{467892A3-FD70-4046-A7B8-1DD9EBF000B6}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="8_{0AAFFBA4-7A17-4274-9ECD-974DB7A7961E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8FFA876F-2D2D-4934-A32F-0A31F6040E97}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{5CBB6DD7-3CC5-4E66-A43F-40443A3B5A51}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6928" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6934" uniqueCount="104">
   <si>
     <t>SEASON</t>
   </si>
@@ -314,6 +314,24 @@
   </si>
   <si>
     <t>=concatenar("00"';C3)</t>
+  </si>
+  <si>
+    <t>22500165</t>
+  </si>
+  <si>
+    <t>22500171</t>
+  </si>
+  <si>
+    <t>22500163</t>
+  </si>
+  <si>
+    <t>22500166</t>
+  </si>
+  <si>
+    <t>22500160</t>
+  </si>
+  <si>
+    <t>22500159</t>
   </si>
 </sst>
 </file>
@@ -5081,8 +5099,8 @@
       <c r="B170" s="4">
         <v>45964</v>
       </c>
-      <c r="C170" s="5">
-        <v>22500159</v>
+      <c r="C170" s="5" t="s">
+        <v>103</v>
       </c>
       <c r="D170" s="5"/>
       <c r="E170" s="5" t="s">
@@ -5108,8 +5126,8 @@
       <c r="B171" s="4">
         <v>45964</v>
       </c>
-      <c r="C171" s="5">
-        <v>22500160</v>
+      <c r="C171" s="5" t="s">
+        <v>102</v>
       </c>
       <c r="D171" s="5"/>
       <c r="E171" s="5" t="s">
@@ -5189,8 +5207,8 @@
       <c r="B174" s="4">
         <v>45964</v>
       </c>
-      <c r="C174" s="5">
-        <v>22500163</v>
+      <c r="C174" s="5" t="s">
+        <v>100</v>
       </c>
       <c r="D174" s="5"/>
       <c r="E174" s="5" t="s">
@@ -5243,8 +5261,8 @@
       <c r="B176" s="4">
         <v>45965</v>
       </c>
-      <c r="C176" s="5">
-        <v>22500165</v>
+      <c r="C176" s="5" t="s">
+        <v>98</v>
       </c>
       <c r="D176" s="5"/>
       <c r="E176" s="5" t="s">
@@ -5270,8 +5288,8 @@
       <c r="B177" s="4">
         <v>45965</v>
       </c>
-      <c r="C177" s="5">
-        <v>22500166</v>
+      <c r="C177" s="5" t="s">
+        <v>101</v>
       </c>
       <c r="D177" s="5"/>
       <c r="E177" s="5" t="s">
@@ -5405,8 +5423,8 @@
       <c r="B182" s="4">
         <v>45966</v>
       </c>
-      <c r="C182" s="5">
-        <v>22500171</v>
+      <c r="C182" s="5" t="s">
+        <v>99</v>
       </c>
       <c r="D182" s="5"/>
       <c r="E182" s="5" t="s">
@@ -5425,189 +5443,221 @@
       <c r="J182" s="5"/>
       <c r="K182" s="5"/>
     </row>
-    <row r="183" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A183" t="s">
-        <v>7</v>
-      </c>
-      <c r="B183" s="1">
+    <row r="183" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A183" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B183" s="4">
         <v>45966</v>
       </c>
-      <c r="C183" s="2">
+      <c r="C183" s="5">
         <v>22500172</v>
       </c>
-      <c r="E183" s="2" t="s">
+      <c r="D183" s="5"/>
+      <c r="E183" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="F183" s="2" t="s">
+      <c r="F183" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="G183" s="2" t="s">
+      <c r="G183" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="H183" s="2" t="s">
+      <c r="H183" s="5" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="184" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A184" t="s">
-        <v>7</v>
-      </c>
-      <c r="B184" s="1">
+      <c r="I183" s="5"/>
+      <c r="J183" s="5"/>
+      <c r="K183" s="5"/>
+    </row>
+    <row r="184" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A184" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B184" s="4">
         <v>45966</v>
       </c>
-      <c r="C184" s="2">
+      <c r="C184" s="5">
         <v>22500173</v>
       </c>
-      <c r="E184" s="2" t="s">
+      <c r="D184" s="5"/>
+      <c r="E184" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="F184" s="2" t="s">
+      <c r="F184" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="G184" s="2" t="s">
+      <c r="G184" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="H184" s="2" t="s">
+      <c r="H184" s="5" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="185" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A185" t="s">
-        <v>7</v>
-      </c>
-      <c r="B185" s="1">
+      <c r="I184" s="5"/>
+      <c r="J184" s="5"/>
+      <c r="K184" s="5"/>
+    </row>
+    <row r="185" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A185" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B185" s="4">
         <v>45966</v>
       </c>
-      <c r="C185" s="2">
+      <c r="C185" s="5">
         <v>22500174</v>
       </c>
-      <c r="E185" s="2" t="s">
+      <c r="D185" s="5"/>
+      <c r="E185" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="F185" s="2" t="s">
+      <c r="F185" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="G185" s="2" t="s">
+      <c r="G185" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="H185" s="2" t="s">
+      <c r="H185" s="5" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="186" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A186" t="s">
-        <v>7</v>
-      </c>
-      <c r="B186" s="1">
+      <c r="I185" s="5"/>
+      <c r="J185" s="5"/>
+      <c r="K185" s="5"/>
+    </row>
+    <row r="186" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A186" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B186" s="4">
         <v>45966</v>
       </c>
-      <c r="C186" s="2">
+      <c r="C186" s="5">
         <v>22500175</v>
       </c>
-      <c r="E186" s="2" t="s">
+      <c r="D186" s="5"/>
+      <c r="E186" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="F186" s="2" t="s">
+      <c r="F186" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="G186" s="2" t="s">
+      <c r="G186" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="H186" s="2" t="s">
+      <c r="H186" s="5" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="187" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A187" t="s">
-        <v>7</v>
-      </c>
-      <c r="B187" s="1">
+      <c r="I186" s="5"/>
+      <c r="J186" s="5"/>
+      <c r="K186" s="5"/>
+    </row>
+    <row r="187" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A187" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B187" s="4">
         <v>45966</v>
       </c>
-      <c r="C187" s="2">
+      <c r="C187" s="5">
         <v>22500176</v>
       </c>
-      <c r="E187" s="2" t="s">
+      <c r="D187" s="5"/>
+      <c r="E187" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="F187" s="2" t="s">
+      <c r="F187" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="G187" s="2" t="s">
+      <c r="G187" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="H187" s="2" t="s">
+      <c r="H187" s="5" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="188" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A188" t="s">
-        <v>7</v>
-      </c>
-      <c r="B188" s="1">
+      <c r="I187" s="5"/>
+      <c r="J187" s="5"/>
+      <c r="K187" s="5"/>
+    </row>
+    <row r="188" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A188" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B188" s="4">
         <v>45966</v>
       </c>
-      <c r="C188" s="2">
+      <c r="C188" s="5">
         <v>22500177</v>
       </c>
-      <c r="E188" s="2" t="s">
+      <c r="D188" s="5"/>
+      <c r="E188" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F188" s="2" t="s">
+      <c r="F188" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G188" s="2" t="s">
+      <c r="G188" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="H188" s="2" t="s">
+      <c r="H188" s="5" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="189" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A189" t="s">
-        <v>7</v>
-      </c>
-      <c r="B189" s="1">
+      <c r="I188" s="5"/>
+      <c r="J188" s="5"/>
+      <c r="K188" s="5"/>
+    </row>
+    <row r="189" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A189" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B189" s="4">
         <v>45966</v>
       </c>
-      <c r="C189" s="2">
+      <c r="C189" s="5">
         <v>22500178</v>
       </c>
-      <c r="E189" s="2" t="s">
+      <c r="D189" s="5"/>
+      <c r="E189" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F189" s="2" t="s">
+      <c r="F189" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G189" s="2" t="s">
+      <c r="G189" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="H189" s="2" t="s">
+      <c r="H189" s="5" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="190" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A190" t="s">
-        <v>7</v>
-      </c>
-      <c r="B190" s="1">
+      <c r="I189" s="5"/>
+      <c r="J189" s="5"/>
+      <c r="K189" s="5"/>
+    </row>
+    <row r="190" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A190" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B190" s="4">
         <v>45966</v>
       </c>
-      <c r="C190" s="2">
+      <c r="C190" s="5">
         <v>22500179</v>
       </c>
-      <c r="E190" s="2" t="s">
+      <c r="D190" s="5"/>
+      <c r="E190" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="F190" s="2" t="s">
+      <c r="F190" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="G190" s="2" t="s">
+      <c r="G190" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="H190" s="2" t="s">
+      <c r="H190" s="5" t="s">
         <v>13</v>
       </c>
+      <c r="I190" s="5"/>
+      <c r="J190" s="5"/>
+      <c r="K190" s="5"/>
     </row>
     <row r="191" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
